--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484124_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484124_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.577</v>
+        <v>5.1367</v>
       </c>
       <c r="E2" t="n">
-        <v>2.3443</v>
+        <v>1.409</v>
       </c>
       <c r="F2" t="n">
-        <v>4.2327</v>
+        <v>3.7277</v>
       </c>
       <c r="G2" t="n">
         <v>4.9452</v>
@@ -610,13 +610,13 @@
         <v>2.3806</v>
       </c>
       <c r="S2" t="n">
-        <v>3.631</v>
+        <v>2.1907</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1654</v>
+        <v>1.2301</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4656</v>
+        <v>0.9606</v>
       </c>
       <c r="V2" t="n">
         <v>-0.2138</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>X. ANDREU GARI</t>
+          <t>P. CAMÍ GALERA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.2251</v>
+        <v>4.6894</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1224</v>
+        <v>0.7356</v>
       </c>
       <c r="F3" t="n">
-        <v>3.1028</v>
+        <v>3.9538</v>
       </c>
       <c r="G3" t="n">
-        <v>3.3645</v>
+        <v>-0.5285</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5543</v>
+        <v>-1.381</v>
       </c>
       <c r="I3" t="n">
-        <v>3.9189</v>
+        <v>0.8524</v>
       </c>
       <c r="J3" t="n">
-        <v>2.7943</v>
+        <v>-2.3296</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.0297</v>
+        <v>-2.2167</v>
       </c>
       <c r="L3" t="n">
-        <v>2.8241</v>
+        <v>-0.1128</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5702</v>
+        <v>1.801</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5246</v>
+        <v>0.8358</v>
       </c>
       <c r="O3" t="n">
-        <v>1.0948</v>
+        <v>0.9653</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5952</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.1822</v>
+        <v>-2.9758</v>
       </c>
       <c r="R3" t="n">
-        <v>2.7774</v>
+        <v>2.1822</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0634</v>
+        <v>0.5824</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5103</v>
+        <v>0.3459</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5531</v>
+        <v>0.2365</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.7979000000000001</v>
+        <v>5.4291</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>5.6951</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. CAMÍ GALERA</t>
+          <t>X. ANDREU GARI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2551</v>
+        <v>4.0375</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1656</v>
+        <v>0.8786</v>
       </c>
       <c r="F4" t="n">
-        <v>3.4208</v>
+        <v>3.1589</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.5285</v>
+        <v>3.3645</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.381</v>
+        <v>-0.5543</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8524</v>
+        <v>3.9189</v>
       </c>
       <c r="J4" t="n">
-        <v>-2.3296</v>
+        <v>2.7943</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.2167</v>
+        <v>-0.0297</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.1128</v>
+        <v>2.8241</v>
       </c>
       <c r="M4" t="n">
-        <v>1.801</v>
+        <v>0.5702</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8358</v>
+        <v>-0.5246</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9653</v>
+        <v>1.0948</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.7935</v>
+        <v>0.5952</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.9758</v>
+        <v>-2.1822</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1822</v>
+        <v>2.7774</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8519</v>
+        <v>0.8757</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5554</v>
+        <v>0.2665</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2965</v>
+        <v>0.6092</v>
       </c>
       <c r="V4" t="n">
-        <v>5.4291</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="W4" t="n">
-        <v>5.6951</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.266</v>
+        <v>-0.7979000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. ELLENA VICENTE</t>
+          <t>T. LLOBERA BIBILONI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9441</v>
+        <v>2.478</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2036</v>
+        <v>0.2673</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7405</v>
+        <v>2.2107</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0499</v>
+        <v>1.0334</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3829</v>
+        <v>1.794</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4327</v>
+        <v>-0.7605</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3306</v>
+        <v>0.9256</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3682</v>
+        <v>2.2432</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0376</v>
+        <v>-1.3177</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3805</v>
+        <v>0.1079</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0147</v>
+        <v>-0.4493</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3951</v>
+        <v>0.5572</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1903</v>
+        <v>0.1984</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.1822</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1903</v>
+        <v>2.3806</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0696</v>
+        <v>0.0397</v>
       </c>
       <c r="T5" t="n">
-        <v>0.873</v>
+        <v>0.3175</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1966</v>
+        <v>-0.2778</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.266</v>
+        <v>1.2065</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. LLOBERA BIBILONI</t>
+          <t>A. ELLENA VICENTE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1482</v>
+        <v>1.8366</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.838</v>
+        <v>1.1242</v>
       </c>
       <c r="F6" t="n">
-        <v>1.9862</v>
+        <v>0.7124</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0334</v>
+        <v>-0.0499</v>
       </c>
       <c r="H6" t="n">
-        <v>1.794</v>
+        <v>0.3829</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7605</v>
+        <v>-0.4327</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9256</v>
+        <v>0.3306</v>
       </c>
       <c r="K6" t="n">
-        <v>2.2432</v>
+        <v>0.3682</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.3177</v>
+        <v>-0.0376</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1079</v>
+        <v>-0.3805</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4493</v>
+        <v>0.0147</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5572</v>
+        <v>-0.3951</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1984</v>
+        <v>1.1903</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.1822</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3806</v>
+        <v>1.1903</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2901</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7877999999999999</v>
+        <v>0.7936</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5023</v>
+        <v>0.1686</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2065</v>
+        <v>-0.266</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. LLABRES TUGORES</t>
+          <t>M. COLL JANER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0582</v>
+        <v>0.0412</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.6683</v>
+        <v>-0.3647</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7265</v>
+        <v>0.4059</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7845</v>
+        <v>-0.5748</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.6072</v>
+        <v>-1.0633</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8227</v>
+        <v>0.4884</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.753</v>
+        <v>-0.5797</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.753</v>
+        <v>-0.66</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.0803</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9685</v>
+        <v>0.0049</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1458</v>
+        <v>-0.4032</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8227</v>
+        <v>0.4081</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5952</v>
+        <v>0.3968</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5871</v>
+        <v>0.3968</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8508</v>
+        <v>-0.0468</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8106</v>
+        <v>-0.051</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0401</v>
+        <v>0.0042</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6032</v>
+        <v>0.266</v>
       </c>
       <c r="W7" t="n">
         <v>0.266</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.8692</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. COLL JANER</t>
+          <t>P. LLABRES TUGORES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.043</v>
+        <v>-0.896</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3647</v>
+        <v>-2.2578</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3217</v>
+        <v>1.3618</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5748</v>
+        <v>-0.7845</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.0633</v>
+        <v>-1.6072</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4884</v>
+        <v>0.8227</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5797</v>
+        <v>-1.753</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.66</v>
+        <v>-1.753</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0803</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0049</v>
+        <v>0.9685</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4032</v>
+        <v>0.1458</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4081</v>
+        <v>0.8227</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3968</v>
+        <v>0.5952</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3968</v>
+        <v>1.5871</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1309</v>
+        <v>-0.1035</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.051</v>
+        <v>0.2211</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0799</v>
+        <v>-0.3246</v>
       </c>
       <c r="V8" t="n">
-        <v>0.266</v>
+        <v>-0.6032</v>
       </c>
       <c r="W8" t="n">
         <v>0.266</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.8692</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. AGUILO RODRIGUEZ</t>
+          <t>P. FLUXA PAYERAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0877</v>
+        <v>-0.9789</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.1059</v>
+        <v>-3.0724</v>
       </c>
       <c r="F9" t="n">
-        <v>2.0183</v>
+        <v>2.0935</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.648</v>
+        <v>-1.6747</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.3734</v>
+        <v>-1.6526</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2746</v>
+        <v>-0.0221</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.9526</v>
+        <v>-2.1202</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.3929</v>
+        <v>-1.405</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5597</v>
+        <v>-0.7153</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3046</v>
+        <v>0.4455</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0195</v>
+        <v>-0.2477</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2851</v>
+        <v>0.6932</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9919</v>
+        <v>0.5952</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9919</v>
+        <v>-1.1903</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9838</v>
+        <v>1.7855</v>
       </c>
       <c r="S9" t="n">
-        <v>1.1716</v>
+        <v>0.1006</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5726</v>
+        <v>0.2381</v>
       </c>
       <c r="U9" t="n">
-        <v>0.599</v>
+        <v>-0.1375</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6032</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.8692</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. FLUXA PAYERAS</t>
+          <t>L. SANCHEZ MORENO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.902</v>
+        <v>-1.5356</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.9113</v>
+        <v>-4.3864</v>
       </c>
       <c r="F10" t="n">
-        <v>2.0093</v>
+        <v>2.8508</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.6747</v>
+        <v>-2.381</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.6526</v>
+        <v>1.0225</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0221</v>
+        <v>-3.4035</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.1202</v>
+        <v>-4.2525</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.405</v>
+        <v>0.3884</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7153</v>
+        <v>-4.6409</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4455</v>
+        <v>1.8715</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2477</v>
+        <v>0.6342</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6932</v>
+        <v>1.2374</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5952</v>
+        <v>1.5871</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1903</v>
+        <v>-0.9919</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7855</v>
+        <v>2.579</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8225</v>
+        <v>-0.2097</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6008</v>
+        <v>-0.0112</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2217</v>
+        <v>-0.1985</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.532</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.8692</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.4012</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L. SANCHEZ MORENO</t>
+          <t>M. AGUILO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3552</v>
+        <v>-1.6797</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.9816</v>
+        <v>-3.3894</v>
       </c>
       <c r="F11" t="n">
-        <v>2.6264</v>
+        <v>1.7096</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.381</v>
+        <v>-2.648</v>
       </c>
       <c r="H11" t="n">
-        <v>1.0225</v>
+        <v>-2.3734</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.4035</v>
+        <v>-0.2746</v>
       </c>
       <c r="J11" t="n">
-        <v>-4.2525</v>
+        <v>-2.9526</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3884</v>
+        <v>-2.3929</v>
       </c>
       <c r="L11" t="n">
-        <v>-4.6409</v>
+        <v>-0.5597</v>
       </c>
       <c r="M11" t="n">
-        <v>1.8715</v>
+        <v>0.3046</v>
       </c>
       <c r="N11" t="n">
-        <v>0.6342</v>
+        <v>0.0195</v>
       </c>
       <c r="O11" t="n">
-        <v>1.2374</v>
+        <v>0.2851</v>
       </c>
       <c r="P11" t="n">
-        <v>1.5871</v>
+        <v>0.9919</v>
       </c>
       <c r="Q11" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R11" t="n">
-        <v>2.579</v>
+        <v>1.9838</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0293</v>
+        <v>0.5796</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6064000000000001</v>
+        <v>0.2892</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.423</v>
+        <v>0.2904</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.532</v>
+        <v>-0.6032</v>
       </c>
       <c r="W11" t="n">
-        <v>0.8692</v>
+        <v>0.266</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.4012</v>
+        <v>-0.8692</v>
       </c>
     </row>
     <row r="12">
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.2082</v>
+        <v>-2.9588</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.9881</v>
+        <v>-4.7387</v>
       </c>
       <c r="F12" t="n">
         <v>1.7799</v>
@@ -1390,10 +1390,10 @@
         <v>2.579</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2607</v>
+        <v>-0.0113</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0511</v>
+        <v>0.3005</v>
       </c>
       <c r="U12" t="n">
         <v>-0.3119</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.611600000000003</v>
+        <v>10.1704</v>
       </c>
       <c r="E13" t="n">
-        <v>-15.3532</v>
+        <v>-13.7947</v>
       </c>
       <c r="F13" t="n">
-        <v>23.9651</v>
+        <v>23.965</v>
       </c>
       <c r="G13" t="n">
         <v>-1.753400000000001</v>
@@ -1438,7 +1438,7 @@
         <v>-3.0487</v>
       </c>
       <c r="I13" t="n">
-        <v>1.295399999999999</v>
+        <v>1.2954</v>
       </c>
       <c r="J13" t="n">
         <v>-8.552800000000001</v>
@@ -1450,10 +1450,10 @@
         <v>-4.9564</v>
       </c>
       <c r="M13" t="n">
-        <v>6.799300000000001</v>
+        <v>6.7993</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5478</v>
+        <v>0.5477999999999998</v>
       </c>
       <c r="O13" t="n">
         <v>6.2519</v>
@@ -1468,13 +1468,13 @@
         <v>21.8223</v>
       </c>
       <c r="S13" t="n">
-        <v>3.401</v>
+        <v>4.959600000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>2.3816</v>
+        <v>3.9403</v>
       </c>
       <c r="U13" t="n">
-        <v>1.0191</v>
+        <v>1.0192</v>
       </c>
       <c r="V13" t="n">
         <v>2.004499999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.7198</v>
+        <v>3.311</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6225000000000001</v>
+        <v>-0.8058999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>4.0973</v>
+        <v>4.1169</v>
       </c>
       <c r="G14" t="n">
         <v>0.2984</v>
@@ -1546,13 +1546,13 @@
         <v>2.3806</v>
       </c>
       <c r="S14" t="n">
-        <v>2.2236</v>
+        <v>0.8148</v>
       </c>
       <c r="T14" t="n">
-        <v>2.1031</v>
+        <v>0.6747</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1206</v>
+        <v>0.1401</v>
       </c>
       <c r="V14" t="n">
         <v>2.7929</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.1594</v>
+        <v>3.2182</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.4809</v>
+        <v>-0.0727</v>
       </c>
       <c r="F15" t="n">
-        <v>3.6403</v>
+        <v>3.2909</v>
       </c>
       <c r="G15" t="n">
         <v>3.4639</v>
@@ -1624,13 +1624,13 @@
         <v>2.579</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2147</v>
+        <v>0.2734</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8161</v>
+        <v>-0.408</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0308</v>
+        <v>0.6814</v>
       </c>
       <c r="V15" t="n">
         <v>-1.1143</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0412</v>
+        <v>1.5216</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8164</v>
+        <v>1.0205</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2247</v>
+        <v>0.5011</v>
       </c>
       <c r="G16" t="n">
         <v>1.6902</v>
@@ -1702,13 +1702,13 @@
         <v>0.3968</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0458</v>
+        <v>-0.5654</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2494</v>
+        <v>-0.0453</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7964</v>
+        <v>-0.5201</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. ALIAGA CHECA</t>
+          <t>A. LATORRE SEGURA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2535</v>
+        <v>0.0202</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1725</v>
+        <v>0.0202</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0809</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.237</v>
+        <v>0.0202</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.635</v>
+        <v>0.0202</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8719</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.2693</v>
+        <v>0.0202</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.9922</v>
+        <v>0.0202</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7229</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5062</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3572</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0.149</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7935</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7855</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3373</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.1678</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8305</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.1143</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.3803</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. LATORRE SEGURA</t>
+          <t>M. ALIAGA CHECA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0202</v>
+        <v>-0.3545</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0202</v>
+        <v>-0.8478</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>0.4933</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0202</v>
+        <v>0.237</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0202</v>
+        <v>-0.635</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>0.8719</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0202</v>
+        <v>-0.2693</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0202</v>
+        <v>-0.9922</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.7229</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>0.5062</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>0.3572</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>0.149</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.7935</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.7855</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-0.2706</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.1475</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>-0.4181</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-1.1143</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.3803</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0316</v>
+        <v>-0.882</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.9433</v>
+        <v>-2.8412</v>
       </c>
       <c r="F19" t="n">
-        <v>1.9116</v>
+        <v>1.9592</v>
       </c>
       <c r="G19" t="n">
         <v>1.412</v>
@@ -1936,13 +1936,13 @@
         <v>1.5871</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3311</v>
+        <v>-0.1814</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1926</v>
+        <v>-0.0906</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1384</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="V19" t="n">
         <v>-0.7239</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7378</v>
+        <v>-1.964</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.6872</v>
+        <v>-2.9933</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9494</v>
+        <v>1.0293</v>
       </c>
       <c r="G20" t="n">
         <v>-1.1583</v>
@@ -2014,13 +2014,13 @@
         <v>1.7855</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3832</v>
+        <v>-0.6093</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0625</v>
+        <v>-0.2436</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4457</v>
+        <v>-0.3657</v>
       </c>
       <c r="V20" t="n">
         <v>-0.9899</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.1567</v>
+        <v>-2.1381</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.2536</v>
+        <v>-3.5394</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0969</v>
+        <v>1.4013</v>
       </c>
       <c r="G21" t="n">
         <v>-1.5809</v>
@@ -2092,13 +2092,13 @@
         <v>1.7855</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8683999999999999</v>
+        <v>0.1502</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7423999999999999</v>
+        <v>-0.0282</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.126</v>
+        <v>0.1784</v>
       </c>
       <c r="V21" t="n">
         <v>-1.501</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.9334</v>
+        <v>-4.182</v>
       </c>
       <c r="E22" t="n">
-        <v>-7.3734</v>
+        <v>-6.4551</v>
       </c>
       <c r="F22" t="n">
-        <v>1.44</v>
+        <v>2.2731</v>
       </c>
       <c r="G22" t="n">
         <v>-0.846</v>
@@ -2170,13 +2170,13 @@
         <v>2.579</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.443</v>
+        <v>-0.6915</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.6096</v>
+        <v>-0.6914</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8333</v>
+        <v>-0.0001</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2558</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.9462</v>
+        <v>-5.1215</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.8583</v>
+        <v>-7.4502</v>
       </c>
       <c r="F23" t="n">
-        <v>1.9122</v>
+        <v>2.3288</v>
       </c>
       <c r="G23" t="n">
         <v>-1.7831</v>
@@ -2248,13 +2248,13 @@
         <v>1.9838</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1053</v>
+        <v>-0.2806</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7423999999999999</v>
+        <v>-0.3343</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3629</v>
+        <v>0.0537</v>
       </c>
       <c r="V23" t="n">
         <v>1.9018</v>
@@ -2281,16 +2281,16 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.611599999999999</v>
+        <v>-6.5711</v>
       </c>
       <c r="E24" t="n">
-        <v>-23.9651</v>
+        <v>-23.9649</v>
       </c>
       <c r="F24" t="n">
-        <v>15.3533</v>
+        <v>17.3939</v>
       </c>
       <c r="G24" t="n">
-        <v>1.7534</v>
+        <v>1.753399999999999</v>
       </c>
       <c r="H24" t="n">
         <v>3.0486</v>
@@ -2326,16 +2326,16 @@
         <v>16.8628</v>
       </c>
       <c r="S24" t="n">
-        <v>-3.4012</v>
+        <v>-1.3604</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.0191</v>
+        <v>-1.0192</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.3818</v>
+        <v>-0.3412000000000001</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.0045</v>
+        <v>-2.004500000000001</v>
       </c>
       <c r="W24" t="n">
         <v>5.676</v>
